--- a/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/vanessa_hernandez_gifseguridad_com_mx/Documents/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{475B19B9-2B22-4035-B9AD-111D0E36E1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{66415CC7-3276-4D76-91C3-B60F0EFA58BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/vanessa_hernandez_gifseguridad_com_mx/Documents/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66415CC7-3276-4D76-91C3-B60F0EFA58BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D173C1D6-2CB7-4B35-8CB7-550B67BFF370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>09-0001-02</t>
   </si>
@@ -65,6 +65,12 @@
     <t>ROSAS ROSAS LUIS ENRIQUE</t>
   </si>
   <si>
+    <t>09-0024-02</t>
+  </si>
+  <si>
+    <t>BOHNE LOPEZ CINTIA STEPHANIE</t>
+  </si>
+  <si>
     <t>09-0244-03</t>
   </si>
   <si>
@@ -161,16 +167,16 @@
     <t>MEDINA ALVAREZ KARLA ITZEL</t>
   </si>
   <si>
+    <t>09-0410-03</t>
+  </si>
+  <si>
+    <t>CORREA MARTINEZ JOSE LUIS</t>
+  </si>
+  <si>
     <t>15-0016-03</t>
   </si>
   <si>
     <t>OSORIO MIRANDA REYNA</t>
-  </si>
-  <si>
-    <t>15-0023-03</t>
-  </si>
-  <si>
-    <t>ALAMILLO CHAVEZ RAYMUNDO</t>
   </si>
   <si>
     <t>15-0024-03</t>
@@ -583,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
@@ -707,7 +713,7 @@
         <v>21</v>
       </c>
       <c r="C11">
-        <v>1068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -718,7 +724,7 @@
         <v>23</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -916,6 +922,17 @@
         <v>59</v>
       </c>
       <c r="C30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31">
         <v>0</v>
       </c>
     </row>

--- a/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/vanessa_hernandez_gifseguridad_com_mx/Documents/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D173C1D6-2CB7-4B35-8CB7-550B67BFF370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27AE4032-0A1D-4D0E-A102-6B446D7CCDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>09-0001-02</t>
   </si>
@@ -95,12 +95,6 @@
     <t>HERNANDEZ SOSA JOSE GUADALUPE</t>
   </si>
   <si>
-    <t>09-0368-03</t>
-  </si>
-  <si>
-    <t>ESPINOZA RUIZ ROSA MARIA</t>
-  </si>
-  <si>
     <t>09-0369-03</t>
   </si>
   <si>
@@ -125,12 +119,6 @@
     <t>ITURBIDE JIMENEZ JUAN JESUS</t>
   </si>
   <si>
-    <t>09-0394-03</t>
-  </si>
-  <si>
-    <t>SANTOS ARIAS ANTONIO</t>
-  </si>
-  <si>
     <t>09-0397-03</t>
   </si>
   <si>
@@ -161,16 +149,16 @@
     <t>SILVA ROMERO JACQUELINE</t>
   </si>
   <si>
-    <t>09-0408-03</t>
-  </si>
-  <si>
-    <t>MEDINA ALVAREZ KARLA ITZEL</t>
-  </si>
-  <si>
     <t>09-0410-03</t>
   </si>
   <si>
     <t>CORREA MARTINEZ JOSE LUIS</t>
+  </si>
+  <si>
+    <t>09-0411-03</t>
+  </si>
+  <si>
+    <t>QUINTANA GONZALEZ URIEL</t>
   </si>
   <si>
     <t>15-0016-03</t>
@@ -589,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
@@ -647,7 +635,7 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>782</v>
+        <v>848</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -713,7 +701,7 @@
         <v>21</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -724,7 +712,7 @@
         <v>23</v>
       </c>
       <c r="C12">
-        <v>1068</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -911,28 +899,6 @@
         <v>57</v>
       </c>
       <c r="C29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31">
         <v>0</v>
       </c>
     </row>

--- a/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/vanessa_hernandez_gifseguridad_com_mx/Documents/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27AE4032-0A1D-4D0E-A102-6B446D7CCDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5527363B-ACEC-4D70-9E6E-2B9F99D880F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>09-0001-02</t>
   </si>
@@ -140,7 +140,7 @@
     <t>09-0406-03</t>
   </si>
   <si>
-    <t>RIVERA  FUENTES  EVELYN JAZMIN</t>
+    <t>RIVERA FUENTES EVELYN JAZMIN</t>
   </si>
   <si>
     <t>09-0407-03</t>
@@ -161,6 +161,12 @@
     <t>QUINTANA GONZALEZ URIEL</t>
   </si>
   <si>
+    <t>09-0412-03</t>
+  </si>
+  <si>
+    <t>SOTO SOLORZANO JOAQUIN</t>
+  </si>
+  <si>
     <t>15-0016-03</t>
   </si>
   <si>
@@ -201,6 +207,12 @@
   </si>
   <si>
     <t>SEVILLA MENDEZ JULIO CESAR</t>
+  </si>
+  <si>
+    <t>09-0326-03</t>
+  </si>
+  <si>
+    <t>MIGUEL GARCIA JULIAN</t>
   </si>
   <si>
     <t>09-0347-03</t>
@@ -577,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
@@ -635,7 +647,7 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>848</v>
+        <v>796</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -899,6 +911,28 @@
         <v>57</v>
       </c>
       <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31">
         <v>0</v>
       </c>
     </row>

--- a/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/vanessa_hernandez_gifseguridad_com_mx/Documents/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5527363B-ACEC-4D70-9E6E-2B9F99D880F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD0C3D27-9F14-4BC5-B96A-1676ED67AD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>09-0001-02</t>
   </si>
@@ -143,22 +143,10 @@
     <t>RIVERA FUENTES EVELYN JAZMIN</t>
   </si>
   <si>
-    <t>09-0407-03</t>
-  </si>
-  <si>
-    <t>SILVA ROMERO JACQUELINE</t>
-  </si>
-  <si>
     <t>09-0410-03</t>
   </si>
   <si>
     <t>CORREA MARTINEZ JOSE LUIS</t>
-  </si>
-  <si>
-    <t>09-0411-03</t>
-  </si>
-  <si>
-    <t>QUINTANA GONZALEZ URIEL</t>
   </si>
   <si>
     <t>09-0412-03</t>
@@ -589,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
@@ -911,28 +899,6 @@
         <v>57</v>
       </c>
       <c r="C29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31">
         <v>0</v>
       </c>
     </row>

--- a/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/vanessa_hernandez_gifseguridad_com_mx/Documents/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD0C3D27-9F14-4BC5-B96A-1676ED67AD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{71092B33-E6C6-4FBC-AED8-0E995B10398B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>09-0001-02</t>
   </si>
@@ -155,16 +155,22 @@
     <t>SOTO SOLORZANO JOAQUIN</t>
   </si>
   <si>
+    <t>09-0416-03</t>
+  </si>
+  <si>
+    <t>MENDOZA CABALLERO GERARDO</t>
+  </si>
+  <si>
     <t>15-0016-03</t>
   </si>
   <si>
     <t>OSORIO MIRANDA REYNA</t>
   </si>
   <si>
-    <t>15-0024-03</t>
-  </si>
-  <si>
-    <t>SANCHEZ VARGAS ISAIAS</t>
+    <t>15-0025-03</t>
+  </si>
+  <si>
+    <t>COLIN MENDEZ JUAN MANUEL</t>
   </si>
   <si>
     <t>09-0004-02</t>
@@ -577,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
@@ -899,6 +905,17 @@
         <v>57</v>
       </c>
       <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30">
         <v>0</v>
       </c>
     </row>

--- a/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
@@ -8,27 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/vanessa_hernandez_gifseguridad_com_mx/Documents/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71092B33-E6C6-4FBC-AED8-0E995B10398B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B980AD40-1275-46E5-BA7C-BA151204E7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -167,10 +154,10 @@
     <t>OSORIO MIRANDA REYNA</t>
   </si>
   <si>
-    <t>15-0025-03</t>
-  </si>
-  <si>
-    <t>COLIN MENDEZ JUAN MANUEL</t>
+    <t>15-0026-03</t>
+  </si>
+  <si>
+    <t>ZACARIAS GARCIA MARELY</t>
   </si>
   <si>
     <t>09-0004-02</t>

--- a/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/vanessa_hernandez_gifseguridad_com_mx/Documents/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B980AD40-1275-46E5-BA7C-BA151204E7B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{043928AE-AFF2-4D9D-8228-96B7E0611D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>09-0001-02</t>
   </si>
@@ -148,16 +161,22 @@
     <t>MENDOZA CABALLERO GERARDO</t>
   </si>
   <si>
+    <t>09-0418-03</t>
+  </si>
+  <si>
+    <t>VALENCIA GARCIA GUSTAVO</t>
+  </si>
+  <si>
     <t>15-0016-03</t>
   </si>
   <si>
     <t>OSORIO MIRANDA REYNA</t>
   </si>
   <si>
-    <t>15-0026-03</t>
-  </si>
-  <si>
-    <t>ZACARIAS GARCIA MARELY</t>
+    <t>15-0027-03</t>
+  </si>
+  <si>
+    <t>GONZALEZ FLORES EDITH</t>
   </si>
   <si>
     <t>09-0004-02</t>
@@ -570,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
@@ -903,6 +922,17 @@
         <v>59</v>
       </c>
       <c r="C30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31">
         <v>0</v>
       </c>
     </row>

--- a/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
@@ -8,32 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/vanessa_hernandez_gifseguridad_com_mx/Documents/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{043928AE-AFF2-4D9D-8228-96B7E0611D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDBD0392-A47B-4B60-9F35-1D767CC46E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>09-0001-02</t>
   </si>
@@ -113,12 +100,6 @@
     <t>BUSTAMANTE ARAGON OSCAR</t>
   </si>
   <si>
-    <t>09-0391-03</t>
-  </si>
-  <si>
-    <t>ITURBIDE JIMENEZ JUAN JESUS</t>
-  </si>
-  <si>
     <t>09-0397-03</t>
   </si>
   <si>
@@ -161,10 +142,22 @@
     <t>MENDOZA CABALLERO GERARDO</t>
   </si>
   <si>
-    <t>09-0418-03</t>
-  </si>
-  <si>
-    <t>VALENCIA GARCIA GUSTAVO</t>
+    <t>09-0419-03</t>
+  </si>
+  <si>
+    <t>RIVERA MEZA MARIA AURELIA</t>
+  </si>
+  <si>
+    <t>09-0420-03</t>
+  </si>
+  <si>
+    <t>LUZ GONZALEZ MARICRUZ</t>
+  </si>
+  <si>
+    <t>09-0421-03</t>
+  </si>
+  <si>
+    <t>HUERTA GUTIERREZ MARCO ANTONIO</t>
   </si>
   <si>
     <t>15-0016-03</t>
@@ -589,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
@@ -933,6 +926,17 @@
         <v>61</v>
       </c>
       <c r="C31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32">
         <v>0</v>
       </c>
     </row>

--- a/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/vanessa_hernandez_gifseguridad_com_mx/Documents/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDBD0392-A47B-4B60-9F35-1D767CC46E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8B5DC4B-93CB-405C-9104-929EBE072316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>09-0001-02</t>
   </si>
@@ -100,12 +100,6 @@
     <t>BUSTAMANTE ARAGON OSCAR</t>
   </si>
   <si>
-    <t>09-0397-03</t>
-  </si>
-  <si>
-    <t>VALLADARES PEREZ ALICIA</t>
-  </si>
-  <si>
     <t>09-0403-03</t>
   </si>
   <si>
@@ -136,12 +130,6 @@
     <t>SOTO SOLORZANO JOAQUIN</t>
   </si>
   <si>
-    <t>09-0416-03</t>
-  </si>
-  <si>
-    <t>MENDOZA CABALLERO GERARDO</t>
-  </si>
-  <si>
     <t>09-0419-03</t>
   </si>
   <si>
@@ -166,10 +154,10 @@
     <t>OSORIO MIRANDA REYNA</t>
   </si>
   <si>
-    <t>15-0027-03</t>
-  </si>
-  <si>
-    <t>GONZALEZ FLORES EDITH</t>
+    <t>15-0028-03</t>
+  </si>
+  <si>
+    <t>GUTIERREZ SALGADO AARON ALESSANDRO</t>
   </si>
   <si>
     <t>09-0004-02</t>
@@ -582,10 +570,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
@@ -915,28 +903,6 @@
         <v>59</v>
       </c>
       <c r="C30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" t="s">
-        <v>63</v>
-      </c>
-      <c r="C32">
         <v>0</v>
       </c>
     </row>

--- a/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/vanessa_hernandez_gifseguridad_com_mx/Documents/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8B5DC4B-93CB-405C-9104-929EBE072316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCA46D79-81F1-4A13-A8FD-4BF8FFA70491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -142,10 +142,10 @@
     <t>LUZ GONZALEZ MARICRUZ</t>
   </si>
   <si>
-    <t>09-0421-03</t>
-  </si>
-  <si>
-    <t>HUERTA GUTIERREZ MARCO ANTONIO</t>
+    <t>09-0423-03</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ DAMIAN HUGO RICARDO</t>
   </si>
   <si>
     <t>15-0016-03</t>
@@ -172,12 +172,6 @@
     <t>SANTANA CHAVEZ SALVADOR</t>
   </si>
   <si>
-    <t>09-0160-03</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ HERNANDEZ DIONICIO</t>
-  </si>
-  <si>
     <t>09-0243-03</t>
   </si>
   <si>
@@ -200,6 +194,12 @@
   </si>
   <si>
     <t>RUIZ FUENTES DULCE GEOVANNY</t>
+  </si>
+  <si>
+    <t>09-0374-03</t>
+  </si>
+  <si>
+    <t>VEGA CORTEZ ABIGAIL</t>
   </si>
 </sst>
 </file>

--- a/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
+++ b/Vista/uploads/documentosContabilidad/infonavitNQUINCENAL .xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gifseguridad2014-my.sharepoint.com/personal/vanessa_hernandez_gifseguridad_com_mx/Documents/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCA46D79-81F1-4A13-A8FD-4BF8FFA70491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F98E23A-B53B-4C2A-8343-8AFB09BEC175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
